--- a/cypress/fixtures/CaptAccionistas.xlsx
+++ b/cypress/fixtures/CaptAccionistas.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
   <si>
     <t>AggRef</t>
   </si>
@@ -70,15 +70,6 @@
   </si>
   <si>
     <t>FechaRef</t>
-  </si>
-  <si>
-    <t>010219903312600000</t>
-  </si>
-  <si>
-    <t>18/12/2026</t>
-  </si>
-  <si>
-    <t>234684684687468</t>
   </si>
   <si>
     <t>ESTADOS UNIDOS DE AMERICA</t>
@@ -181,12 +172,6 @@
   </si>
   <si>
     <t>ESTADOUNIDENSE</t>
-  </si>
-  <si>
-    <t>123456789</t>
-  </si>
-  <si>
-    <t>123456789123456</t>
   </si>
   <si>
     <t>Guatemala</t>
@@ -3576,7 +3561,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="2" width="17.63"/>
-    <col customWidth="1" min="5" max="5" width="14.88"/>
+    <col customWidth="1" min="5" max="5" width="15.75"/>
     <col customWidth="1" min="8" max="8" width="26.63"/>
   </cols>
   <sheetData>
@@ -3629,15 +3614,12 @@
       <c r="Z1" s="6"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
-        <v>13</v>
+      <c r="A2" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""001"""),"0101 1997 33037001")</f>
+        <v>0101 1997 33037001</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>14</v>
-      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -3667,19 +3649,20 @@
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="9"/>
-      <c r="E3" s="11" t="s">
-        <v>15</v>
+      <c r="E3" s="11" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """") &amp; ""03"""),"010119973303703")</f>
+        <v>010119973303703</v>
       </c>
       <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
+      <c r="G3" s="11"/>
       <c r="H3" s="11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
@@ -31631,33 +31614,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C2" s="9"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="s">
+      <c r="B3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C3" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="C2" s="9"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -36674,57 +36657,57 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="5" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="B2" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -36744,37 +36727,39 @@
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
       <c r="C3" s="11" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="M3" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="K3" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>50</v>
+      <c r="N3" s="11" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("RIGHT(SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """"), 9)
+"),"199733037")</f>
+        <v>199733037</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -53744,7 +53729,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="14.0"/>
-    <col customWidth="1" min="2" max="2" width="14.88"/>
+    <col customWidth="1" min="2" max="2" width="16.75"/>
     <col customWidth="1" min="3" max="3" width="26.63"/>
     <col customWidth="1" min="6" max="6" width="14.88"/>
     <col customWidth="1" min="7" max="7" width="16.25"/>
@@ -53770,53 +53755,55 @@
         <v>12</v>
       </c>
       <c r="F1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="8"/>
-      <c r="B2" s="8" t="s">
-        <v>51</v>
+      <c r="B2" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """")
+&amp; ""02"""),"010119973303702")</f>
+        <v>010119973303702</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">

--- a/cypress/fixtures/CaptAccionistas.xlsx
+++ b/cypress/fixtures/CaptAccionistas.xlsx
@@ -3615,8 +3615,8 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""001"""),"0101 1997 33037001")</f>
-        <v>0101 1997 33037001</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""001"""),"0101 1997 33074001")</f>
+        <v>0101 1997 33074001</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3650,8 +3650,8 @@
       <c r="C3" s="10"/>
       <c r="D3" s="9"/>
       <c r="E3" s="11" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """") &amp; ""03"""),"010119973303703")</f>
-        <v>010119973303703</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """") &amp; ""03"""),"010119973307403")</f>
+        <v>010119973307403</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="11"/>
@@ -36755,8 +36755,8 @@
       </c>
       <c r="N3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("RIGHT(SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """"), 9)
-"),"199733037")</f>
-        <v>199733037</v>
+"),"199733074")</f>
+        <v>199733074</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>14</v>
@@ -53777,8 +53777,8 @@
       <c r="A2" s="8"/>
       <c r="B2" s="8" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """")
-&amp; ""02"""),"010119973303702")</f>
-        <v>010119973303702</v>
+&amp; ""02"""),"010119973307402")</f>
+        <v>010119973307402</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>13</v>

--- a/cypress/fixtures/CaptAccionistas.xlsx
+++ b/cypress/fixtures/CaptAccionistas.xlsx
@@ -3562,6 +3562,7 @@
   <cols>
     <col customWidth="1" min="1" max="2" width="17.63"/>
     <col customWidth="1" min="5" max="5" width="15.75"/>
+    <col customWidth="1" min="7" max="7" width="16.75"/>
     <col customWidth="1" min="8" max="8" width="26.63"/>
   </cols>
   <sheetData>
@@ -3615,8 +3616,8 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""001"""),"0101 1997 33074001")</f>
-        <v>0101 1997 33074001</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""001"""),"0101 1997 33102001")</f>
+        <v>0101 1997 33102001</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3645,16 +3646,16 @@
       <c r="Z2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="3"/>
+      <c r="A3" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""003"""),"0101 1997 33102003")</f>
+        <v>0101 1997 33102003</v>
+      </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="9"/>
-      <c r="E3" s="11" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """") &amp; ""03"""),"010119973307403")</f>
-        <v>010119973307403</v>
-      </c>
+      <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="11"/>
+      <c r="G3" s="9"/>
       <c r="H3" s="11" t="s">
         <v>13</v>
       </c>
@@ -36755,8 +36756,8 @@
       </c>
       <c r="N3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("RIGHT(SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """"), 9)
-"),"199733074")</f>
-        <v>199733074</v>
+"),"199733102")</f>
+        <v>199733102</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>14</v>
@@ -53777,8 +53778,8 @@
       <c r="A2" s="8"/>
       <c r="B2" s="8" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """")
-&amp; ""02"""),"010119973307402")</f>
-        <v>010119973307402</v>
+&amp; ""02"""),"010119973310202")</f>
+        <v>010119973310202</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>13</v>

--- a/cypress/fixtures/CaptAccionistas.xlsx
+++ b/cypress/fixtures/CaptAccionistas.xlsx
@@ -3616,8 +3616,8 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""001"""),"0101 1997 33102001")</f>
-        <v>0101 1997 33102001</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""001"""),"0101 1997 33133001")</f>
+        <v>0101 1997 33133001</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3647,8 +3647,8 @@
     </row>
     <row r="3">
       <c r="A3" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""003"""),"0101 1997 33102003")</f>
-        <v>0101 1997 33102003</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""003"""),"0101 1997 33133003")</f>
+        <v>0101 1997 33133003</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -36756,8 +36756,8 @@
       </c>
       <c r="N3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("RIGHT(SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """"), 9)
-"),"199733102")</f>
-        <v>199733102</v>
+"),"199733133")</f>
+        <v>199733133</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>14</v>
@@ -53778,8 +53778,8 @@
       <c r="A2" s="8"/>
       <c r="B2" s="8" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """")
-&amp; ""02"""),"010119973310202")</f>
-        <v>010119973310202</v>
+&amp; ""02"""),"010119973313302")</f>
+        <v>010119973313302</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>13</v>

--- a/cypress/fixtures/CaptAccionistas.xlsx
+++ b/cypress/fixtures/CaptAccionistas.xlsx
@@ -3616,8 +3616,8 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""001"""),"0101 1997 33133001")</f>
-        <v>0101 1997 33133001</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""001"""),"0101 1997 33141001")</f>
+        <v>0101 1997 33141001</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3647,8 +3647,8 @@
     </row>
     <row r="3">
       <c r="A3" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""003"""),"0101 1997 33133003")</f>
-        <v>0101 1997 33133003</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""003"""),"0101 1997 33141003")</f>
+        <v>0101 1997 33141003</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -36756,8 +36756,8 @@
       </c>
       <c r="N3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("RIGHT(SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """"), 9)
-"),"199733133")</f>
-        <v>199733133</v>
+"),"199733141")</f>
+        <v>199733141</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>14</v>
@@ -53778,8 +53778,8 @@
       <c r="A2" s="8"/>
       <c r="B2" s="8" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """")
-&amp; ""02"""),"010119973313302")</f>
-        <v>010119973313302</v>
+&amp; ""02"""),"010119973314102")</f>
+        <v>010119973314102</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>13</v>

--- a/cypress/fixtures/CaptAccionistas.xlsx
+++ b/cypress/fixtures/CaptAccionistas.xlsx
@@ -3562,6 +3562,7 @@
   <cols>
     <col customWidth="1" min="1" max="2" width="17.63"/>
     <col customWidth="1" min="5" max="5" width="15.75"/>
+    <col customWidth="1" min="7" max="7" width="16.75"/>
     <col customWidth="1" min="8" max="8" width="26.63"/>
   </cols>
   <sheetData>
@@ -3615,8 +3616,8 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""001"""),"0101 1997 33037001")</f>
-        <v>0101 1997 33037001</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""001"""),"0101 1997 33102001")</f>
+        <v>0101 1997 33102001</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3645,16 +3646,16 @@
       <c r="Z2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="3"/>
+      <c r="A3" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""003"""),"0101 1997 33102003")</f>
+        <v>0101 1997 33102003</v>
+      </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="9"/>
-      <c r="E3" s="11" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """") &amp; ""03"""),"010119973303703")</f>
-        <v>010119973303703</v>
-      </c>
+      <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="11"/>
+      <c r="G3" s="9"/>
       <c r="H3" s="11" t="s">
         <v>13</v>
       </c>
@@ -36755,8 +36756,8 @@
       </c>
       <c r="N3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("RIGHT(SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """"), 9)
-"),"199733037")</f>
-        <v>199733037</v>
+"),"199733102")</f>
+        <v>199733102</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>14</v>
@@ -53777,8 +53778,8 @@
       <c r="A2" s="8"/>
       <c r="B2" s="8" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """")
-&amp; ""02"""),"010119973303702")</f>
-        <v>010119973303702</v>
+&amp; ""02"""),"010119973310202")</f>
+        <v>010119973310202</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>13</v>

--- a/cypress/fixtures/CaptAccionistas.xlsx
+++ b/cypress/fixtures/CaptAccionistas.xlsx
@@ -147,13 +147,13 @@
     <t>UbiSegNacRef</t>
   </si>
   <si>
-    <t>Lieonel Jr</t>
+    <t>Juan Carlos</t>
   </si>
   <si>
-    <t>iñigo</t>
+    <t>Julian</t>
   </si>
   <si>
-    <t>martinez</t>
+    <t>Alvarez</t>
   </si>
   <si>
     <t>Masculino</t>
@@ -273,7 +273,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -300,6 +300,9 @@
     <xf borderId="0" fillId="4" fontId="3" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="4" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -3616,8 +3619,8 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""001"""),"0101 1997 33158001")</f>
-        <v>0101 1997 33158001</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("LEFT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), 15) &amp; ""001"""),"0101 1997 33227001")</f>
+        <v>0101 1997 33227001</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3647,8 +3650,8 @@
     </row>
     <row r="3">
       <c r="A3" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2"")  &amp; ""003"""),"0101 1997 33158003")</f>
-        <v>0101 1997 33158003</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("LEFT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), 15) &amp; ""003"""),"0101 1997 33227003")</f>
+        <v>0101 1997 33227003</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -3880,7 +3883,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3"/>
-      <c r="B11" s="10"/>
+      <c r="B11" s="12"/>
       <c r="C11" s="10"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -36736,7 +36739,7 @@
         <v>40</v>
       </c>
       <c r="G3" s="9"/>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I3" s="11" t="s">
@@ -36756,8 +36759,8 @@
       </c>
       <c r="N3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("RIGHT(SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """"), 9)
-"),"199733158")</f>
-        <v>199733158</v>
+"),"733227000")</f>
+        <v>733227000</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>14</v>
@@ -53777,9 +53780,8 @@
     <row r="2">
       <c r="A2" s="8"/>
       <c r="B2" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUBSTITUTE(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), "" "", """")
-&amp; ""02"""),"010119973315802")</f>
-        <v>010119973315802</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("LEFT(IMPORTRANGE(""1_xriSLIwwVjPl8SPQz6HpPENpfWiztH_Avw6PdiYhY8"", ""'0 Cliente'!B2""), 15) &amp; ""02"""),"0101 1997 3322702")</f>
+        <v>0101 1997 3322702</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>13</v>
